--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,24 +591,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,32 +618,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, GCP, MLOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
+          <t>https://www.indeed.com/viewjob?jk=ce062c1221d36aca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, GCP, MLOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce062c1221d36aca</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Hadoop Developer-6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
+          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hadoop Developer-6</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d96d2facf0c62b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d96d2facf0c62b</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Airflow ML Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,85 +1851,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Teradata Developer-5</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Airflow ML Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Data Architect-5</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6408ada685f1f82</t>
+          <t>https://www.indeed.com/viewjob?jk=955ac0b1ad8a879b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.9</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955ac0b1ad8a879b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hadoop Developer-6</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hadoop Developer-6</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Burbank, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d96d2facf0c62b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d96d2facf0c62b</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,15 +1353,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,15 +1388,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-6</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Airflow ML Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1755,111 +1755,6 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Teradata Developer-5</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Airflow ML Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
@@ -1343,25 +1343,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Airflow ML Engineer</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,15 +1746,190 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior GCP Kubernetes Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Teradata Developer-5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Airflow ML Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,7 +608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, GCP, MLOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce062c1221d36aca</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Burbank, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d96d2facf0c62b</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Airflow ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,777 +1161,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>DevOps Engineer - Remote (Blockchain)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HT Archery</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Solutions Engineer II - Networking</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Okta IAM Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior SRE (GCP)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior SRE (GCP)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior GCP Kubernetes Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Teradata Developer-5</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Airflow ML Engineer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
+          <t>https://www.indeed.com/viewjob?jk=74f0c78139f81162</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Validation Engineer (ML)</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,15 +478,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35.4</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aa9d1342b93a57e</t>
+          <t>https://www.indeed.com/viewjob?jk=955ac0b1ad8a879b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955ac0b1ad8a879b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Airflow ML Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,215 +986,40 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>DevOps Engineer - Remote (Blockchain)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HT Archery</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Python / Linux-7</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Snowflake Admin-8</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Teradata Developer-5</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Airflow ML Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>DevOps Engineer - Remote (Blockchain)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HT Archery</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=74f0c78139f81162</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Covista</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=4adc00b1af8ae9f8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Airflow ML Engineer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Remote (Blockchain)</t>
+          <t>Airflow ML Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HT Archery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,15 +1011,50 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - Remote (Blockchain)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>HT Archery</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=74f0c78139f81162</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=b912b59e0b8d6118</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Covista</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4adc00b1af8ae9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Airflow ML Engineer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Remote (Blockchain)</t>
+          <t>Airflow ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HT Archery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f0c78139f81162</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,87 +503,87 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a1223c9ae7d10ef4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b912b59e0b8d6118</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,112 +731,112 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=6129a30842f97a0c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Oracle, MySQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=866c80a990582061</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,110 +951,320 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>SAP AI Business Services Consultant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Python / Linux-7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Snowflake Admin-8</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Contractor</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Westford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Teradata Developer-5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Airflow ML Engineer</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>CA, US USA</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D24" t="n">
         <v>10.4</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,280 +503,280 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1223c9ae7d10ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e490bc759502c67</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d00686588a7f2f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=29bc94ef9fa6d728</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Senior Architect, Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=c334a7201b918676</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=ab2c2352d8a6b2e5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8254910b2e0a9ccf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=774ed20e20da648c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Architect, Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>20.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6129a30842f97a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b3aecc3f0c2918bd</t>
         </is>
       </c>
     </row>
@@ -788,125 +788,125 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, Azure, Event Hubs, GCP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866c80a990582061</t>
+          <t>https://www.indeed.com/viewjob?jk=a52c3f44e5a3ffad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Kinesis, RDS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=a176b1d110af7c59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=a1223c9ae7d10ef4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc1bee1da622032</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,322 +951,2702 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Beyond Finance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d644470785695c9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b0630815d9f1ee</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=04f21ddd72acad2d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RAPP</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=322259901e919b33</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RAPP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1b59271e2e7306a1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=758e31bc763ea430</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Kafka, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=515da2564d1d2849</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Airflow ML Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Jade Global</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bandwidth</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f22e811beee03bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer | The Points Guy</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Red Ventures</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=483258c9c4ba7328</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>JUUL Labs</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Polars, Data Modeling, dbt</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b49523fc43db3539</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HackerRank Careers</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7cb53b2278767490</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Baker Hill Solutions</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Event Hubs, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d05e81347a9f3ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer-7</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Terraform MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c791c3f73dcee4ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PandaDoc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=329171b36cb94b8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Architect, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Credera</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bebeee11b3071962</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Architect, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Credera</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=485d2e6de1e8a086</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Architect, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Credera</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bfe3e20a463eab6</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Architect, Software Engineering</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Credera</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44e55eaa7ba6dddd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Flexport</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=441c085efd50fec8</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Data Platform</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Latitude AI</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, dbt, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31d0a022197dd7b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Snowflake &amp; Data Platform Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dff6531dd274cbf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>GCP AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data-Driven Applications</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vectra AI</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, ELT</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde81135b1d2415c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Quality Systems Specialist</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>North Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (ML Engineering)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, MLflow, AKS, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27775c7b5198786e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc1447f0d619c40b</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a369ab2eae275c5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e447be457217f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ccefe6b4cf39fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17dbbfe7334c8ce4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6915a31a656eea7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7217e6f4e824dd90</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CNH Industrial</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Global KTech</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd25c09387615839</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Associate/Programmatic AdTech Engineer (Forensic Services practice)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Charles River Associates</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be13ca4a9a8cc28d</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SAP AI Business Services Consultant</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (Linux)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Quantifind</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c97b7d55357997ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37fe7aa557db1f8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intern: Financial Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=148277e432f8a247</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Python / Linux-7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Contractor</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Westford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b756426841c0b5e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Snowflake Admin-8</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>RAPP</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Kafka, CI/CD, Jenkins, CodeBuild</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b88ac0d6454a8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure (Federal)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
         <v>10.4</v>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9482dc007d5f456</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer - Hybrid</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rithum</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, Terraform, Docker, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09e319f44bbefcf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>6sense</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Hive, Scala, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1d1937310481ac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Solutions Architect – Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=041435b48d6f6f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SecurityScorecard</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc8b92a08f94ce52</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DigitalOcean</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788d6cc73ba81698</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior AI Operations (AI Ops) Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Navan</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6c986c8da176b02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Vestmark</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wakefield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Splunk, Git</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=205593dc85af0e57</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>DigitalOcean</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab40b456a5ed1302</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DigitalOcean</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ada0e4ff27142e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>DigitalOcean</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ac52f1c6b3389ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>DigitalOcean</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ae192cb5db2c1ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d54db8a56bcc0ca9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, Currents</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SQS, SNS, RDS, Scala, Kafka, MongoDB, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57676c626db37b70</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, Currents</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SQS, SNS, RDS, Scala, Kafka, MongoDB, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa498de985d99c6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer, Currents</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Braze</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SQS, SNS, RDS, Scala, Kafka, MongoDB, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a04534d00c6c5fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41b6cb8dfc375ac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer, Code Generation</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c31a324a7fdd053b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SQL/Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Teradata Developer-5</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Taskrabbit</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=955f461b0fdcc829</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Technical Services Engineer, Infrastructure - Weekend</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2649842ffc3e9b0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=809cf2b07d76fc6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer | Growth &amp; Transformation</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Red Ventures</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78b69a4f32a0c224</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sr. Network Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LendingTree</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=172d803032cd9cf3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,410 +503,410 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Senior Consultant - Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Torq</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, BigQuery, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e490bc759502c67</t>
+          <t>https://www.indeed.com/viewjob?jk=627b28d27cdd515d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d00686588a7f2f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4189a27528fb7891</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bc94ef9fa6d728</t>
+          <t>https://www.indeed.com/viewjob?jk=3efe0be0fa4e69bd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Architect, Data</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c334a7201b918676</t>
+          <t>https://www.indeed.com/viewjob?jk=71a92327666e2e49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab2c2352d8a6b2e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a176b1d110af7c59</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8254910b2e0a9ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=5c601ba0fc4929fd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Linqia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Kafka, PostgreSQL, MySQL, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774ed20e20da648c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cb97d3cce0e619d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Architect, Data</t>
+          <t>Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>VIANT TECHNOLOGY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3aecc3f0c2918bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ca59effc4fffa0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Sparksoft Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, ECS, Azure, Event Hubs, GCP</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52c3f44e5a3ffad</t>
+          <t>https://www.indeed.com/viewjob?jk=177c1fa16655c829</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a176b1d110af7c59</t>
+          <t>https://www.indeed.com/viewjob?jk=37a9ad20c3bd407d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1223c9ae7d10ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=77f0f7b6c9ae04a1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>Azure, Databricks, Delta Live Tables, Hadoop, HDFS, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc1bee1da622032</t>
+          <t>https://www.indeed.com/viewjob?jk=cf3f90d5535fb27e</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Beyond Finance</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Medallion Architecture, GCP, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d644470785695c9</t>
+          <t>https://www.indeed.com/viewjob?jk=998a00ad8ab8e32b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b0630815d9f1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=91226c24b6879a61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,99 +1046,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f21ddd72acad2d</t>
+          <t>https://www.indeed.com/viewjob?jk=9979c4161b7d1a64</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=24f511432f1f9bcf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RAPP</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322259901e919b33</t>
+          <t>https://www.indeed.com/viewjob?jk=445036056e0d881d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RAPP</t>
+          <t>Beyond Finance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,63 +1147,63 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b59271e2e7306a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d644470785695c9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758e31bc763ea430</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfe3ff5d4f466b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Kafka, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,732 +1231,732 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515da2564d1d2849</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b0630815d9f1ee</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=04f21ddd72acad2d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bandwidth</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f22e811beee03bab</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e54103834693c8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483258c9c4ba7328</t>
+          <t>https://www.indeed.com/viewjob?jk=3fac75658b888d65</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Polars, Data Modeling, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49523fc43db3539</t>
+          <t>https://www.indeed.com/viewjob?jk=673567339b696c66</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, Redshift, ECS, RDS, MapReduce, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cb53b2278767490</t>
+          <t>https://www.indeed.com/viewjob?jk=2b38e1d32dc000f7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Baker Hill Solutions</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d05e81347a9f3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=e09d4d83502b87c9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=d998d88fdaab892c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=87e86206d218fd74</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c791c3f73dcee4ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f3262badaab123</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>Datavant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329171b36cb94b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=86f647da7c2c02a8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>PLUME</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, EMR, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebeee11b3071962</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf09b6ef4e5ea86</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d2e6de1e8a086</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Data Integration Engineer - Healthcare Data Infrastructure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfe3e20a463eab6</t>
+          <t>https://www.indeed.com/viewjob?jk=26e790bb3385ccac</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Architect, Software Engineering</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e55eaa7ba6dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=9fef5ce599643ddc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7b4de46d5550c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Flexport</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441c085efd50fec8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c134558da63d227</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Latitude AI</t>
+          <t>RAPP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, dbt, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31d0a022197dd7b9</t>
+          <t>https://www.indeed.com/viewjob?jk=322259901e919b33</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Snowflake &amp; Data Platform Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>RAPP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff6531dd274cbf5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b59271e2e7306a1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=f5304017ab38b24d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data-Driven Applications</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde81135b1d2415c</t>
+          <t>https://www.indeed.com/viewjob?jk=e33980dcad1911f3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,334 +1966,334 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (ML Engineering)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, MLflow, AKS, Airflow, Git</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27775c7b5198786e</t>
+          <t>https://www.indeed.com/viewjob?jk=da1852f1725f9882</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1447f0d619c40b</t>
+          <t>https://www.indeed.com/viewjob?jk=758e31bc763ea430</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Kafka, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a369ab2eae275c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=515da2564d1d2849</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Sr. Data Engineer - Healthcare Data Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e447be457217f98</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95885d69f3a37b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Sr. Data Engineer - Healthcare Data Infrastructure (Texas)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ccefe6b4cf39fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7b2e9802100892</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17dbbfe7334c8ce4</t>
+          <t>https://www.indeed.com/viewjob?jk=885d2a5468ce45a5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6915a31a656eea7e</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd468dc4d752a5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7217e6f4e824dd90</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab11172124e6b35</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=267348cf0105191f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,256 +2302,256 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa39e7e627b5bd04</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0595c928f058fb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data &amp; AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>Chorus Innovations</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd25c09387615839</t>
+          <t>https://www.indeed.com/viewjob?jk=dd35c02d8537b8b6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Associate/Programmatic AdTech Engineer (Forensic Services practice)</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Charles River Associates</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Snowflake, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be13ca4a9a8cc28d</t>
+          <t>https://www.indeed.com/viewjob?jk=c3518c8ad9f0e8d0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c3e6d6624a12591</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer (Linux)</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Scala, PostgreSQL, Jenkins, Maven, Docker, Kubernetes, Jenkins, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97b7d55357997ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0383c17bdd68dc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fe7aa557db1f8b</t>
+          <t>https://www.indeed.com/viewjob?jk=d18f1ce8a33187d6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,662 +2561,662 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148277e432f8a247</t>
+          <t>https://www.indeed.com/viewjob?jk=77760179e0788eac</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=39561230ddbde763</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack (EAA - Compliance)</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, MongoDB, NoSQL, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b756426841c0b5e4</t>
+          <t>https://www.indeed.com/viewjob?jk=483258c9c4ba7328</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Canopy Tax</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=10deefa32e4b8054</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RAPP</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, IAM, RDS, Kafka, CI/CD, Jenkins, CodeBuild</t>
+          <t>AWS, S3, IAM, Scala, PostgreSQL, MySQL, Splunk, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b88ac0d6454a8b</t>
+          <t>https://www.indeed.com/viewjob?jk=b77f18311791c5d8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure (Federal)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, SNS, RDS, GCP, BigQuery, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9482dc007d5f456</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0d326eb1fcf1f3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer - Hybrid</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rithum</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, Terraform, Docker, Kubernetes, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09e319f44bbefcf4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd40900c394646c6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hive, Scala, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1937310481ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5f0c868a2c2e1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Polars, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=b49523fc43db3539</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Architect, Finance &amp; Legal Systems</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=041435b48d6f6f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a3c5fd5fff0345</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SecurityScorecard</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8b92a08f94ce52</t>
+          <t>https://www.indeed.com/viewjob?jk=089044f585e5b515</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+          <t>Junior Solution Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788d6cc73ba81698</t>
+          <t>https://www.indeed.com/viewjob?jk=04062b8d9c7be463</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Operations (AI Ops) Engineer</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Navan</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, Snowflake, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c986c8da176b02</t>
+          <t>https://www.indeed.com/viewjob?jk=f03a7b3e4280c07f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vestmark</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wakefield, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Splunk, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=205593dc85af0e57</t>
+          <t>https://www.indeed.com/viewjob?jk=7cb53b2278767490</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+          <t>QA Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>Kinesis, RDS, Azure, Flume, Spark, Scala, Spark Streaming, Kafka, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab40b456a5ed1302</t>
+          <t>https://www.indeed.com/viewjob?jk=b5650929e9b21133</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ada0e4ff27142e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>Baker Hill Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ac52f1c6b3389ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7d05e81347a9f3ed</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect (Database Migrations Specialist)</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Terraform</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae192cb5db2c1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,427 +3226,4347 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d54db8a56bcc0ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=01e6c14fc4039fec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Currents</t>
+          <t>Senior Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SQS, SNS, RDS, Scala, Kafka, MongoDB, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, DynamoDB, Cassandra, NoSQL, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57676c626db37b70</t>
+          <t>https://www.indeed.com/viewjob?jk=2502a89d47ef5b4e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Currents</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SQS, SNS, RDS, Scala, Kafka, MongoDB, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa498de985d99c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4578fd1a73e718</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer, Currents</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Braze</t>
+          <t>Avetta</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SQS, SNS, RDS, Scala, Kafka, MongoDB, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a04534d00c6c5fc</t>
+          <t>https://www.indeed.com/viewjob?jk=58937da34b860fcf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>PandaDoc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b6cb8dfc375ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=329171b36cb94b8a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer, Code Generation</t>
+          <t>Cloud Engineer (Full Stack / AWS)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Particle41</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31a324a7fdd053b</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1c1838529ad26</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+          <t>https://www.indeed.com/viewjob?jk=f19890b70d192dab</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=f230dc0e6d1e114c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>MuleSoft Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Taskrabbit</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955f461b0fdcc829</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bb5818fbd93d7a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Technical Services Engineer, Infrastructure - Weekend</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, Kubernetes, Python</t>
+          <t>AWS, Athena, Azure, GCP, Spark, PySpark, Scala, Time Travel, dbt, Tableau</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649842ffc3e9b0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3529dbf9c0179ae6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809cf2b07d76fc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=eea74f1dec514506</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Fullstack Engineer | Growth &amp; Transformation</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, DynamoDB, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b69a4f32a0c224</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Network Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>SpyCloud</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6795b407dce62c7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Terraform MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Cloud Engineer, Contract To Hire</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>66degrees</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=457e3685bea4e43d</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Flexport</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=441c085efd50fec8</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Gradient AI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15f0f7a6d40c320f</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Platform/DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c053e495653c0e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ffeb1ee043a99f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Snowflake &amp; Data Platform Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>LendingTree</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Charlotte, NC, US USA</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dff6531dd274cbf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Surt AI</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab5997f135ae7ff6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Surt AI</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ed26f085dbb80ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, GCP, Kafka, MongoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b85fceb8179c41d</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Tebra</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Corona del Mar, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e72db0b65a035f06</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend &amp; Data</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EPIC Kids</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Hadoop, HDFS, Hive, HBase, Spark, Scala, Dimensional Modeling, Kimball, Star Schema, Fact Tables</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1fa918834ca520e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer, Data</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Mercari</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a998dd935be05c4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Investment Compliance Engineeer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Apollo</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>West Monroe</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, YARN, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d56ed709de123ccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>within</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c1b8052c520238e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data-Driven Applications</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Vectra AI</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, ELT</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bde81135b1d2415c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SaaS Platform Architect</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Legion</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4503c0bae2650019</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Konrad Group</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b59276e38a3792d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Quality Systems Specialist</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>North Charleston, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Product</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Art of Problem Solving Academy</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6123e8fb6e4b9c03</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (ML Engineering)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, MLflow, AKS, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27775c7b5198786e</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Exiger</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Athena, S3, RDS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b417041c5e167ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>The Knot Worldwide</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3866528c0c4c42f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Octus</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9917822fb76ec18c</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc1447f0d619c40b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a369ab2eae275c5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e447be457217f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ccefe6b4cf39fcb</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17dbbfe7334c8ce4</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6915a31a656eea7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Analytics Engineer, People Analytics</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7217e6f4e824dd90</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CNH Industrial</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Global KTech</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ripple</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd25c09387615839</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Credit Karma</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f31b874eb934bcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sr. Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=698b540258cfcb66</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer, Machine Learning Platform</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>The New York Times</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, GCP, BigQuery, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04016a73405055c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Data Engineer, Revenue Technology</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>The New York Times</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Data Modeling, ETL, Pentaho, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d68ff54cc645ee45</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Site Reliability/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Origis Energy</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, MySQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30b4bf646bfcd626</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Gallup</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Snowflake, MySQL, DynamoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fad735850fdd422</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6e0bde8c41e20a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer II</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e14efc6b3a547f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Infrastructure</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>GoGuardian</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>El Segundo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8e01663940dc503</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Infrastructure</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GoGuardian</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a18245e7689460dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Graph Databases</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Hone health</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2c345200fd565a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Graph Databases</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Hone health</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0b93aab582e5c5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Flagship Pioneering, Inc.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=994eff426e58131c</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Keeper Security</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>El Dorado Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbac1edd00d90bb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Keeper Security</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5116d23e81868b7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37fe7aa557db1f8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81a07845c3146bdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Cargomatic</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40d4d8e83f705afd</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Python / Linux-7</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Sr Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BeyondTrust</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a615d3d337639a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Chariot Energy</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a757d67b74798878</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Platform DevEx Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Black Canyon Consulting</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75a7e956c12bdc6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Platform DevEx Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Black Canyon Consulting</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=231b3551d1964b47</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Platform DevEx Engineer (DevOps)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Black Canyon Consulting</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04691f1e7d928ccb</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Back-end)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>inversion</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Playa Vista, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MySQL, MongoDB, DynamoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d67473bb44960f85</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Full Stack Developer Contractor</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Westford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Intern: Financial Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>EquipmentShare</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Columbia, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=148277e432f8a247</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Snowflake Admin-8</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>StockX</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
         <v>10.4</v>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Terraform, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Spark Streaming, Kafka, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=269c9b47a6a44cf8</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>InStride</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MongoDB, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7277f852b05ff55f</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Alpaca</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=673a5bf1209ca871</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Alpaca</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757d74e2095c2c31</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc1362387d330626</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Site Reliability</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>BABYLIST</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b9276905ba0f21</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Site Reliability</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BABYLIST</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Emeryville, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ee049b023a70680</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Infrastructure (Federal)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9482dc007d5f456</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=935bb71394d92d60</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a44a84f2f8930db</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>jamf</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c89d1883f151242</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Trivelta</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Redshift, Athena, BigQuery, Scala, Snowflake, ELT, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe224b36114f1f74</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>peregrine technologies</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83c5ad9d6af7101e</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>peregrine technologies</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c90e473beb0de9b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>peregrine technologies</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cb739eafa098172</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>TESSCO</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61dbf36ce450d053</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>FortifyIQ</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Salem, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, MLOps, CI/CD, Airflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2286a631ab81c0c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Software Engineer Go Outdoors</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Brandt Information Services, Inc.</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96e66828bc10e4bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68de55a9dd8f6511</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Frontend</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36be0146f5317a2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior Tableau Analyst</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Keeper Security</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>El Dorado Hills, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d83133d3b54a850e</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior Quality Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Circle.so</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3a0e12ad05e6f6ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Senior Quality Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Circle.so</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8df725374039684f</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Bird Rides</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e321aa62ce282cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>6sense</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Hive, Scala, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1d1937310481ac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, MLOps</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Path Robotics, Inc.</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4cd936db0ee5a06f</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Senior Solutions Architect - Weights &amp; Biases</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MLOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec6fe2aa83e84d26</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer, AI/ML</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Viral Nation</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>IAM, RDS, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57242a1632c106a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Delivery Solution Architect (US)</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Prophecy</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Texas City, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=172d803032cd9cf3</t>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2f8f6b81e67f67a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Delivery Solution Architect (US)</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Prophecy</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83ccd6881ad6a8a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Lantern</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=025d7d48551febf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Software Engineer, Code Generation</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c31a324a7fdd053b</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer, DevOps</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Parloa</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e609c5bc393ab2a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Metrics and Storage- Weights &amp; Biases</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Weights &amp; Biases</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, MySQL, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df212162e0fe3ad2</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SentinelOne</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06ad6be87c6e18e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SentinelOne</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=088631d63b72ebf1</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>IonQ</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Bothell, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=874999787fb11334</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Senior Software Systems Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87ba6300acccca23</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Senior Software Systems Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Aliso Viejo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=094bed05b586255d</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Solutions Architect – Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SQL/Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Teradata Developer-5</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Tableau Engineer</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e80a48ce045ed33</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>AI Architect, Salesforce</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, Snowflake, Terraform</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71fa457437f2101d</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Measurement &amp; Ads</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bbf401730ca7f87</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Taskrabbit</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=955f461b0fdcc829</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Senior AI-Enabled Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>eClinical Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Mansfield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, SQL Server, CI/CD, Docker, Kubernetes, Git, Datadog, Python</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27ad80ec756bf5da</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a176b1d110af7c59</t>
+          <t>https://www.indeed.com/viewjob?jk=5c601ba0fc4929fd</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c601ba0fc4929fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a176b1d110af7c59</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Database Reliability Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VIANT TECHNOLOGY</t>
+          <t>Sparksoft Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9ca59effc4fffa0</t>
+          <t>https://www.indeed.com/viewjob?jk=177c1fa16655c829</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sparksoft Corporation</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=177c1fa16655c829</t>
+          <t>https://www.indeed.com/viewjob?jk=37a9ad20c3bd407d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37a9ad20c3bd407d</t>
+          <t>https://www.indeed.com/viewjob?jk=77f0f7b6c9ae04a1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Data Architect</t>
+          <t>Database Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>VIANT TECHNOLOGY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, IAM, RDS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f0f7b6c9ae04a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c9ca59effc4fffa0</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b0630815d9f1ee</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qualified Health</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Medallion Architecture, GCP, PostgreSQL, MySQL</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998a00ad8ab8e32b</t>
+          <t>https://www.indeed.com/viewjob?jk=04f21ddd72acad2d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Beyond Finance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91226c24b6879a61</t>
+          <t>https://www.indeed.com/viewjob?jk=5d644470785695c9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Medallion Architecture, GCP, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9979c4161b7d1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=998a00ad8ab8e32b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f511432f1f9bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=91226c24b6879a61</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445036056e0d881d</t>
+          <t>https://www.indeed.com/viewjob?jk=9979c4161b7d1a64</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Beyond Finance</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d644470785695c9</t>
+          <t>https://www.indeed.com/viewjob?jk=24f511432f1f9bcf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer (DataOps)</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1191,29 +1191,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfe3ff5d4f466b</t>
+          <t>https://www.indeed.com/viewjob?jk=445036056e0d881d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b0630815d9f1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfe3ff5d4f466b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f21ddd72acad2d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09d4d83502b87c9</t>
+          <t>https://www.indeed.com/viewjob?jk=87e86206d218fd74</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,29 +1466,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d998d88fdaab892c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f3262badaab123</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e86206d218fd74</t>
+          <t>https://www.indeed.com/viewjob?jk=e09d4d83502b87c9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f3262badaab123</t>
+          <t>https://www.indeed.com/viewjob?jk=d998d88fdaab892c</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Integration Engineer - Healthcare Data Infrastructure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=26e790bb3385ccac</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Integration Engineer - Healthcare Data Infrastructure</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qualified Health</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26e790bb3385ccac</t>
+          <t>https://www.indeed.com/viewjob?jk=9fef5ce599643ddc</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fef5ce599643ddc</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7b4de46d5550c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7b4de46d5550c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c134558da63d227</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>RAPP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,24 +1781,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c134558da63d227</t>
+          <t>https://www.indeed.com/viewjob?jk=322259901e919b33</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1821,29 +1821,29 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322259901e919b33</t>
+          <t>https://www.indeed.com/viewjob?jk=1b59271e2e7306a1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RAPP</t>
+          <t>SambaNova Systems</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Scala, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b59271e2e7306a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5304017ab38b24d</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5304017ab38b24d</t>
+          <t>https://www.indeed.com/viewjob?jk=e33980dcad1911f3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SambaNova Systems</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33980dcad1911f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
+          <t>https://www.indeed.com/viewjob?jk=da1852f1725f9882</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, NoSQL</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1852f1725f9882</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=758e31bc763ea430</t>
+          <t>https://www.indeed.com/viewjob?jk=3c3e6d6624a12591</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Spark, Kafka, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=515da2564d1d2849</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab11172124e6b35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Healthcare Data Infrastructure</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Qualified Health</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab95885d69f3a37b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Healthcare Data Infrastructure (Texas)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Qualified Health</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Snowflake, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7b2e9802100892</t>
+          <t>https://www.indeed.com/viewjob?jk=758e31bc763ea430</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Databricks, Spark, Kafka, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885d2a5468ce45a5</t>
+          <t>https://www.indeed.com/viewjob?jk=515da2564d1d2849</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer - Healthcare Data Infrastructure</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd468dc4d752a5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab95885d69f3a37b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Sr. Data Engineer - Healthcare Data Infrastructure (Texas)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>Redshift, RDS, Azure, Data Factory, Databricks, BigQuery, Spark, PySpark, Snowflake, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab11172124e6b35</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7b2e9802100892</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=267348cf0105191f</t>
+          <t>https://www.indeed.com/viewjob?jk=885d2a5468ce45a5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa39e7e627b5bd04</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd468dc4d752a5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0595c928f058fb</t>
+          <t>https://www.indeed.com/viewjob?jk=267348cf0105191f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Chorus Innovations</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd35c02d8537b8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa39e7e627b5bd04</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3518c8ad9f0e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0595c928f058fb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Chorus Innovations</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c3e6d6624a12591</t>
+          <t>https://www.indeed.com/viewjob?jk=dd35c02d8537b8b6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0383c17bdd68dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c3518c8ad9f0e8d0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18f1ce8a33187d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0383c17bdd68dc</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77760179e0788eac</t>
+          <t>https://www.indeed.com/viewjob?jk=d18f1ce8a33187d6</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=77760179e0788eac</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39561230ddbde763</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483258c9c4ba7328</t>
+          <t>https://www.indeed.com/viewjob?jk=39561230ddbde763</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Canopy Tax</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10deefa32e4b8054</t>
+          <t>https://www.indeed.com/viewjob?jk=483258c9c4ba7328</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, PostgreSQL, MySQL, Splunk, Terraform, AWS CloudFormation, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Polars, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77f18311791c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b49523fc43db3539</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Attain</t>
+          <t>Canopy Tax</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, RDS, GCP, BigQuery, Scala, Kafka, MySQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0d326eb1fcf1f3</t>
+          <t>https://www.indeed.com/viewjob?jk=10deefa32e4b8054</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, Scala, PostgreSQL, MySQL, Splunk, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd40900c394646c6</t>
+          <t>https://www.indeed.com/viewjob?jk=b77f18311791c5d8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SNS, RDS, GCP, BigQuery, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5f0c868a2c2e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0d326eb1fcf1f3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Polars, Data Modeling, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49523fc43db3539</t>
+          <t>https://www.indeed.com/viewjob?jk=bd40900c394646c6</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a7b3e4280c07f</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cb53b2278767490</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QA Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,139 +3076,139 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Flume, Spark, Scala, Spark Streaming, Kafka, DataOps, CI/CD</t>
+          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5650929e9b21133</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5f0c868a2c2e1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=f03a7b3e4280c07f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Baker Hill Solutions</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d05e81347a9f3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7cb53b2278767490</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>QA Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>Kinesis, RDS, Azure, Flume, Spark, Scala, Spark Streaming, Kafka, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5650929e9b21133</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e6c14fc4039fec</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Platform</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Baker Hill Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, DynamoDB, Cassandra, NoSQL, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Event Hubs, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502a89d47ef5b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d05e81347a9f3ed</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4578fd1a73e718</t>
+          <t>https://www.indeed.com/viewjob?jk=01e6c14fc4039fec</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Avetta</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, dbt</t>
+          <t>AWS, GCP, BigQuery, DynamoDB, Cassandra, NoSQL, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58937da34b860fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=2502a89d47ef5b4e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329171b36cb94b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4578fd1a73e718</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Full Stack / AWS)</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Particle41</t>
+          <t>Avetta</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, Scala, DynamoDB, CI/CD</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1c1838529ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=58937da34b860fcf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>PandaDoc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19890b70d192dab</t>
+          <t>https://www.indeed.com/viewjob?jk=329171b36cb94b8a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud Engineer (Full Stack / AWS)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Particle41</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Power BI, MLflow, Git, Bitbucket</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f230dc0e6d1e114c</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1c1838529ad26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MuleSoft Architect</t>
+          <t>Sr. Application Integration Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bb5818fbd93d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MuleSoft Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Athena, Azure, GCP, Spark, PySpark, Scala, Time Travel, dbt, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3529dbf9c0179ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bb5818fbd93d7a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Athena, Azure, GCP, Spark, PySpark, Scala, Time Travel, dbt, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea74f1dec514506</t>
+          <t>https://www.indeed.com/viewjob?jk=3529dbf9c0179ae6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6795b407dce62c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=eea74f1dec514506</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,104 +3671,104 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=457e3685bea4e43d</t>
+          <t>https://www.indeed.com/viewjob?jk=6795b407dce62c7f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Flexport</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=441c085efd50fec8</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, GCP, Kafka, MongoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f0f7a6d40c320f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b85fceb8179c41d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c053e495653c0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=15f0f7a6d40c320f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffeb1ee043a99f0</t>
+          <t>https://www.indeed.com/viewjob?jk=e72db0b65a035f06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Snowflake &amp; Data Platform Operations Engineer</t>
+          <t>Software Engineer, Backend &amp; Data</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Hadoop, HDFS, Hive, HBase, Spark, Scala, Dimensional Modeling, Kimball, Star Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff6531dd274cbf5</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa918834ca520e2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
+          <t>https://www.indeed.com/viewjob?jk=457e3685bea4e43d</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Flexport</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5997f135ae7ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=441c085efd50fec8</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed26f085dbb80ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9c053e495653c0e2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, GCP, Kafka, MongoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b85fceb8179c41d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffeb1ee043a99f0</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake &amp; Data Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, Lambda, IAM, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72db0b65a035f06</t>
+          <t>https://www.indeed.com/viewjob?jk=dff6531dd274cbf5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend &amp; Data</t>
+          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Spark, Scala, Dimensional Modeling, Kimball, Star Schema, Fact Tables</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa918834ca520e2</t>
+          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a998dd935be05c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5997f135ae7ff6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed26f085dbb80ff</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,29 +4196,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, YARN, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56ed709de123ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=9a998dd935be05c4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>within</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1b8052c520238e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data-Driven Applications</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, ELT</t>
+          <t>AWS, S3, Azure, GCP, YARN, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde81135b1d2415c</t>
+          <t>https://www.indeed.com/viewjob?jk=d56ed709de123ccd</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>within</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4503c0bae2650019</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1b8052c520238e</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Software Engineer - Data-Driven Applications</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>Vectra AI</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59276e38a3792d8</t>
+          <t>https://www.indeed.com/viewjob?jk=bde81135b1d2415c</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=4503c0bae2650019</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6123e8fb6e4b9c03</t>
+          <t>https://www.indeed.com/viewjob?jk=b59276e38a3792d8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (ML Engineering)</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, MLflow, AKS, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27775c7b5198786e</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b417041c5e167ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=6123e8fb6e4b9c03</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist (ML Engineering)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>The Knot Worldwide</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, MLflow, AKS, Airflow, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3866528c0c4c42f5</t>
+          <t>https://www.indeed.com/viewjob?jk=27775c7b5198786e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Octus</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,69 +4546,69 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Athena, S3, RDS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9917822fb76ec18c</t>
+          <t>https://www.indeed.com/viewjob?jk=b417041c5e167ad7</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1447f0d619c40b</t>
+          <t>https://www.indeed.com/viewjob?jk=3866528c0c4c42f5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Software Engineer II, Data &amp; AI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a369ab2eae275c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fd25c09387615839</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e447be457217f98</t>
+          <t>https://www.indeed.com/viewjob?jk=37fe7aa557db1f8b</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ccefe6b4cf39fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1447f0d619c40b</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17dbbfe7334c8ce4</t>
+          <t>https://www.indeed.com/viewjob?jk=a369ab2eae275c5b</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6915a31a656eea7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e447be457217f98</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7217e6f4e824dd90</t>
+          <t>https://www.indeed.com/viewjob?jk=6ccefe6b4cf39fcb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=17dbbfe7334c8ce4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,19 +4871,19 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=6915a31a656eea7e</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=7217e6f4e824dd90</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data &amp; AI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd25c09387615839</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f31b874eb934bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=698b540258cfcb66</t>
+          <t>https://www.indeed.com/viewjob?jk=4f31b874eb934bcd</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning Platform</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04016a73405055c1</t>
+          <t>https://www.indeed.com/viewjob?jk=698b540258cfcb66</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer, Revenue Technology</t>
+          <t>Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Data Modeling, ETL, Pentaho, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, GCP, BigQuery, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68ff54cc645ee45</t>
+          <t>https://www.indeed.com/viewjob?jk=04016a73405055c1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Site Reliability/Data Engineer</t>
+          <t>Data Engineer, Revenue Technology</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Origis Energy</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, MySQL, ETL, CI/CD</t>
+          <t>AWS, GCP, Scala, Data Modeling, ETL, Pentaho, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30b4bf646bfcd626</t>
+          <t>https://www.indeed.com/viewjob?jk=d68ff54cc645ee45</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability/Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Gallup</t>
+          <t>Origis Energy</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Snowflake, MySQL, DynamoDB, Data Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fad735850fdd422</t>
+          <t>https://www.indeed.com/viewjob?jk=30b4bf646bfcd626</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Gallup</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,17 +5176,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Snowflake, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e0bde8c41e20a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7fad735850fdd422</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e14efc6b3a547f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e0bde8c41e20a6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e01663940dc503</t>
+          <t>https://www.indeed.com/viewjob?jk=3e14efc6b3a547f1</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,19 +5291,19 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18245e7689460dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e01663940dc503</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Graph Databases</t>
+          <t>Senior Software Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Hone health</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c345200fd565a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a18245e7689460dc</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b93aab582e5c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c345200fd565a8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer, Graph Databases</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Flagship Pioneering, Inc.</t>
+          <t>Hone health</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=994eff426e58131c</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b93aab582e5c5f</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Flagship Pioneering, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbac1edd00d90bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=994eff426e58131c</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5116d23e81868b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fe7aa557db1f8b</t>
+          <t>https://www.indeed.com/viewjob?jk=81a07845c3146bdc</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a07845c3146bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=40d4d8e83f705afd</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40d4d8e83f705afd</t>
+          <t>https://www.indeed.com/viewjob?jk=fbac1edd00d90bb0</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5116d23e81868b7b</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Platform Engineers</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a615d3d337639a45</t>
+          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chariot Energy</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757d67b74798878</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Platform DevEx Engineer</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a7e956c12bdc6a</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Platform DevEx Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231b3551d1964b47</t>
+          <t>https://www.indeed.com/viewjob?jk=a615d3d337639a45</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Platform DevEx Engineer (DevOps)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Chariot Energy</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+          <t>S3, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04691f1e7d928ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=a757d67b74798878</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Software Engineer III (Back-end)</t>
+          <t>Platform DevEx Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>inversion</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Playa Vista, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67473bb44960f85</t>
+          <t>https://www.indeed.com/viewjob?jk=75a7e956c12bdc6a</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Platform DevEx Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=231b3551d1964b47</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Senior Platform DevEx Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148277e432f8a247</t>
+          <t>https://www.indeed.com/viewjob?jk=04691f1e7d928ccb</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Software Engineer III (Back-end)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>inversion</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Playa Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,42 +5911,42 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=d67473bb44960f85</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>StockX</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Spark Streaming, Kafka, dbt, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,94 +5956,94 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269c9b47a6a44cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>InStride</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7277f852b05ff55f</t>
+          <t>https://www.indeed.com/viewjob?jk=148277e432f8a247</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673a5bf1209ca871</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>StockX</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Spark Streaming, Kafka, dbt, Airflow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757d74e2095c2c31</t>
+          <t>https://www.indeed.com/viewjob?jk=269c9b47a6a44cf8</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,29 +6086,29 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1362387d330626</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0e12ad05e6f6ea</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Site Reliability</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>BABYLIST</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b9276905ba0f21</t>
+          <t>https://www.indeed.com/viewjob?jk=8df725374039684f</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Site Reliability</t>
+          <t>Senior Software Engineer, Measurement &amp; Ads</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>BABYLIST</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee049b023a70680</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbf401730ca7f87</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure (Federal)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9482dc007d5f456</t>
+          <t>https://www.indeed.com/viewjob?jk=e321aa62ce282cdf</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Azure, GCP, Hive, Scala, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935bb71394d92d60</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1937310481ac7</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Data Engineer, MLOps</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a44a84f2f8930db</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd936db0ee5a06f</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>InStride</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c89d1883f151242</t>
+          <t>https://www.indeed.com/viewjob?jk=7277f852b05ff55f</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Trivelta</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Athena, BigQuery, Scala, Snowflake, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe224b36114f1f74</t>
+          <t>https://www.indeed.com/viewjob?jk=673a5bf1209ca871</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>peregrine technologies</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5ad9d6af7101e</t>
+          <t>https://www.indeed.com/viewjob?jk=757d74e2095c2c31</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>peregrine technologies</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90e473beb0de9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1362387d330626</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Senior Software Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>peregrine technologies</t>
+          <t>BABYLIST</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb739eafa098172</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b9276905ba0f21</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Senior Software Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>BABYLIST</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dbf36ce450d053</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee049b023a70680</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer (Remote)</t>
+          <t>Senior Software Engineer, Infrastructure (Federal)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>FortifyIQ</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Salem, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, MLOps, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2286a631ab81c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9482dc007d5f456</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96e66828bc10e4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=935bb71394d92d60</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68de55a9dd8f6511</t>
+          <t>https://www.indeed.com/viewjob?jk=7a44a84f2f8930db</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,34 +6611,34 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36be0146f5317a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c89d1883f151242</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Tableau Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Trivelta</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,29 +6646,29 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, Kinesis, Redshift, Athena, BigQuery, Scala, Snowflake, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83133d3b54a850e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe224b36114f1f74</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>peregrine technologies</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0e12ad05e6f6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5ad9d6af7101e</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>peregrine technologies</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df725374039684f</t>
+          <t>https://www.indeed.com/viewjob?jk=c90e473beb0de9b2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>peregrine technologies</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e321aa62ce282cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb739eafa098172</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hive, Scala, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1937310481ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=61dbf36ce450d053</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, MLOps</t>
+          <t>Data &amp; AI Engineer (Remote)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>FortifyIQ</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salem, MA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, MLOps, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd936db0ee5a06f</t>
+          <t>https://www.indeed.com/viewjob?jk=2286a631ab81c0c7</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Weights &amp; Biases</t>
+          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MLOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec6fe2aa83e84d26</t>
+          <t>https://www.indeed.com/viewjob?jk=68de55a9dd8f6511</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AI Integration Engineer, AI/ML</t>
+          <t>Senior Solutions Architect - Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Viral Nation</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MLOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57242a1632c106a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec6fe2aa83e84d26</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Delivery Solution Architect (US)</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Prophecy</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8f6b81e67f67a4</t>
+          <t>https://www.indeed.com/viewjob?jk=96e66828bc10e4bb</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Delivery Solution Architect (US)</t>
+          <t>AI Integration Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Prophecy</t>
+          <t>Viral Nation</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
+          <t>IAM, RDS, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ccd6881ad6a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=57242a1632c106a7</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Delivery Solution Architect (US)</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Prophecy</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025d7d48551febf2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8f6b81e67f67a4</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer, Code Generation</t>
+          <t>Delivery Solution Architect (US)</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Prophecy</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31a324a7fdd053b</t>
+          <t>https://www.indeed.com/viewjob?jk=83ccd6881ad6a8a9</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, DevOps</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Parloa</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,29 +7066,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e609c5bc393ab2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=025d7d48551febf2</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Metrics and Storage- Weights &amp; Biases</t>
+          <t>Senior Software Engineer, Frontend</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Lila Sciences</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7101,34 +7101,34 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, MySQL, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df212162e0fe3ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=36be0146f5317a2e</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Tableau Analyst</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SentinelOne</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ad6be87c6e18e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d83133d3b54a850e</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Engineer, Code Generation</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>SentinelOne</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,34 +7171,34 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088631d63b72ebf1</t>
+          <t>https://www.indeed.com/viewjob?jk=c31a324a7fdd053b</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Forward Deployed Engineer, DevOps</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Parloa</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,34 +7206,34 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874999787fb11334</t>
+          <t>https://www.indeed.com/viewjob?jk=e609c5bc393ab2a6</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Senior Software Systems Integration Engineer</t>
+          <t>Senior Software Engineer, Metrics and Storage- Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, MySQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ba6300acccca23</t>
+          <t>https://www.indeed.com/viewjob?jk=df212162e0fe3ad2</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Senior Software Systems Integration Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>SentinelOne</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,34 +7276,34 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094bed05b586255d</t>
+          <t>https://www.indeed.com/viewjob?jk=06ad6be87c6e18e7</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>SentinelOne</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=088631d63b72ebf1</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+          <t>https://www.indeed.com/viewjob?jk=874999787fb11334</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Senior Software Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,34 +7381,34 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=87ba6300acccca23</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Tableau Engineer</t>
+          <t>Senior Software Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,34 +7416,34 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e80a48ce045ed33</t>
+          <t>https://www.indeed.com/viewjob?jk=094bed05b586255d</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>AI Architect, Salesforce</t>
+          <t>Solutions Architect – Cloud Platforms</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>First Quality</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, Snowflake, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71fa457437f2101d</t>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Measurement &amp; Ads</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,34 +7486,34 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbf401730ca7f87</t>
+          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Taskrabbit</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955f461b0fdcc829</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Senior AI-Enabled Software Engineer in Test</t>
+          <t>Tableau Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,15 +7556,120 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e80a48ce045ed33</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>AI Architect, Salesforce</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, Snowflake, Terraform</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71fa457437f2101d</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Taskrabbit</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=955f461b0fdcc829</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Senior AI-Enabled Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>eClinical Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Mansfield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, SQL Server, CI/CD, Docker, Kubernetes, Git, Datadog, Python</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27ad80ec756bf5da</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quilt</t>
+          <t>Constant Contact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,17 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c601ba0fc4929fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a176b1d110af7c59</t>
         </is>
       </c>
     </row>
@@ -683,12 +683,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Constant Contact</t>
+          <t>Quilt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a176b1d110af7c59</t>
+          <t>https://www.indeed.com/viewjob?jk=5c601ba0fc4929fd</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
+          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b0630815d9f1ee</t>
+          <t>https://www.indeed.com/viewjob?jk=24f511432f1f9bcf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Medallion Architecture, GCP, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04f21ddd72acad2d</t>
+          <t>https://www.indeed.com/viewjob?jk=998a00ad8ab8e32b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Beyond Finance</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d644470785695c9</t>
+          <t>https://www.indeed.com/viewjob?jk=91226c24b6879a61</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qualified Health</t>
+          <t>eClinical Solutions, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Mansfield, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, Medallion Architecture, GCP, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998a00ad8ab8e32b</t>
+          <t>https://www.indeed.com/viewjob?jk=9979c4161b7d1a64</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Senior Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91226c24b6879a61</t>
+          <t>https://www.indeed.com/viewjob?jk=445036056e0d881d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>Beyond Finance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, Databricks, Spark, Scala, Kafka, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9979c4161b7d1a64</t>
+          <t>https://www.indeed.com/viewjob?jk=5d644470785695c9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Platform Engineer (DataOps)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, Snowflake, PostgreSQL, MongoDB, ETL, ELT, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f511432f1f9bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=4abfe3ff5d4f466b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (DataOps)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445036056e0d881d</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b0630815d9f1ee</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Platform Engineer (DataOps)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Google Cloud Platform, GCP, Flume, Spark, Spark Streaming, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, Unity Catalog, GCP, Sqoop, Flume, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4abfe3ff5d4f466b</t>
+          <t>https://www.indeed.com/viewjob?jk=04f21ddd72acad2d</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote, US)</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openly</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5e54103834693c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e09d4d83502b87c9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fac75658b888d65</t>
+          <t>https://www.indeed.com/viewjob?jk=d998d88fdaab892c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Google Cloud Data Engineer</t>
+          <t>Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>Openly</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Spark, Scala, Kafka, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673567339b696c66</t>
+          <t>https://www.indeed.com/viewjob?jk=c5e54103834693c8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SmartAsset</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, ECS, RDS, MapReduce, Scala, Snowflake, Time Travel</t>
+          <t>AWS, Lambda, S3, IAM, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b38e1d32dc000f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3fac75658b888d65</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Google Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>NMI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e86206d218fd74</t>
+          <t>https://www.indeed.com/viewjob?jk=673567339b696c66</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NetDocuments</t>
+          <t>SmartAsset</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,29 +1466,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, Redshift, ECS, RDS, MapReduce, Scala, Snowflake, Time Travel</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f3262badaab123</t>
+          <t>https://www.indeed.com/viewjob?jk=2b38e1d32dc000f7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e09d4d83502b87c9</t>
+          <t>https://www.indeed.com/viewjob?jk=87e86206d218fd74</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>NetDocuments</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, ECS, IAM, RDS, Azure, HBase, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d998d88fdaab892c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f3262badaab123</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Integration Engineer - Healthcare Data Infrastructure</t>
+          <t>Sr. DevOps Engineer, Cloud Security</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qualified Health</t>
+          <t>CentralReach</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Holmdel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26e790bb3385ccac</t>
+          <t>https://www.indeed.com/viewjob?jk=81e7b4de46d5550c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Data Integration Engineer - Healthcare Data Infrastructure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Qualified Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fef5ce599643ddc</t>
+          <t>https://www.indeed.com/viewjob?jk=26e790bb3385ccac</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Security</t>
+          <t>Software Engineer, Data (L1)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, S3, SQS, SNS, IAM, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e7b4de46d5550c</t>
+          <t>https://www.indeed.com/viewjob?jk=9fef5ce599643ddc</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Governance and QA</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c3e6d6624a12591</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ab11172124e6b35</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=267348cf0105191f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ab11172124e6b35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa39e7e627b5bd04</t>
+          <t>https://www.indeed.com/viewjob?jk=267348cf0105191f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0595c928f058fb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa39e7e627b5bd04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chorus Innovations</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, RDS, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd35c02d8537b8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0595c928f058fb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Chorus Innovations</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,29 +2481,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3518c8ad9f0e8d0</t>
+          <t>https://www.indeed.com/viewjob?jk=dd35c02d8537b8b6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Field Engineer</t>
+          <t>Data Engineer - Governance and QA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Striim</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Data Modeling, dbt, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e0383c17bdd68dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3c3e6d6624a12591</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Software Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d18f1ce8a33187d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c3518c8ad9f0e8d0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Sr Field Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77760179e0788eac</t>
+          <t>https://www.indeed.com/viewjob?jk=4e0383c17bdd68dc</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,94 +2631,94 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=d18f1ce8a33187d6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ROLLER</t>
+          <t>JENSEN HUGHES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39561230ddbde763</t>
+          <t>https://www.indeed.com/viewjob?jk=77760179e0788eac</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer | The Points Guy</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Red Ventures</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483258c9c4ba7328</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JUUL Labs</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Polars, Data Modeling, dbt</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b49523fc43db3539</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Canopy Tax</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Jordan, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10deefa32e4b8054</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, PostgreSQL, MySQL, Splunk, Terraform, AWS CloudFormation, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77f18311791c5d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Attain</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SNS, RDS, GCP, BigQuery, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0d326eb1fcf1f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bd40900c394646c6</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NiCE</t>
+          <t>Man Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sandy, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd40900c394646c6</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5f0c868a2c2e1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>ROLLER</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0a3c5fd5fff0345</t>
+          <t>https://www.indeed.com/viewjob?jk=39561230ddbde763</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Senior Data Engineer | The Points Guy</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Robots &amp; Pencils</t>
+          <t>Red Ventures</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=089044f585e5b515</t>
+          <t>https://www.indeed.com/viewjob?jk=483258c9c4ba7328</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Junior Solution Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>andrew morgan</t>
+          <t>Canopy Tax</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>South Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Scala, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04062b8d9c7be463</t>
+          <t>https://www.indeed.com/viewjob?jk=10deefa32e4b8054</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, Scala, PostgreSQL, MySQL, Splunk, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=b77f18311791c5d8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Lambda, Kinesis, SNS, RDS, GCP, BigQuery, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0d326eb1fcf1f3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Spark, Kafka, Dask, MongoDB, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Polars, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5f0c868a2c2e1</t>
+          <t>https://www.indeed.com/viewjob?jk=b49523fc43db3539</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Application Software Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>K2 Space</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03a7b3e4280c07f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0a3c5fd5fff0345</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HackerRank Careers</t>
+          <t>Robots &amp; Pencils</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, API Gateway, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cb53b2278767490</t>
+          <t>https://www.indeed.com/viewjob?jk=089044f585e5b515</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>QA Platform Engineer</t>
+          <t>Junior Solution Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>andrew morgan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,139 +3181,139 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Flume, Spark, Scala, Spark Streaming, Kafka, DataOps, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Synapse Analytics, Databricks, Scala, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5650929e9b21133</t>
+          <t>https://www.indeed.com/viewjob?jk=04062b8d9c7be463</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Application Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>K2 Space</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=f03a7b3e4280c07f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Baker Hill Solutions</t>
+          <t>HackerRank Careers</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Azure Cosmos DB, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d05e81347a9f3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=7cb53b2278767490</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>QA Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Kinesis, RDS, Azure, Flume, Spark, Scala, Spark Streaming, Kafka, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e6c14fc4039fec</t>
+          <t>https://www.indeed.com/viewjob?jk=b5650929e9b21133</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Platform</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, DynamoDB, Cassandra, NoSQL, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2502a89d47ef5b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure, Engineer II</t>
+          <t>Sr. Application Integration Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Trinity Logistics</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seaford, DE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4578fd1a73e718</t>
+          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Avetta</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, dbt</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58937da34b860fcf</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PandaDoc</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329171b36cb94b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=01e6c14fc4039fec</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Full Stack / AWS)</t>
+          <t>Senior Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Particle41</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, GCP, BigQuery, DynamoDB, Cassandra, NoSQL, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9f1c1838529ad26</t>
+          <t>https://www.indeed.com/viewjob?jk=2502a89d47ef5b4e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Application Integration Engineer</t>
+          <t>Cloud Infrastructure, Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Trinity Logistics</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seaford, DE, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4578fd1a73e718</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MuleSoft Architect</t>
+          <t>Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Avetta</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Kafka, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0bb5818fbd93d7a</t>
+          <t>https://www.indeed.com/viewjob?jk=58937da34b860fcf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Anduril</t>
+          <t>PandaDoc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Athena, Azure, GCP, Spark, PySpark, Scala, Time Travel, dbt, Tableau</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, dbt, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3529dbf9c0179ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=329171b36cb94b8a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>Cloud Engineer (Full Stack / AWS)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Particle41</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9f1c1838529ad26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Risk Data AI/ML Engineer</t>
+          <t>MuleSoft Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Kafka, ELT, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eea74f1dec514506</t>
+          <t>https://www.indeed.com/viewjob?jk=f0bb5818fbd93d7a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Anduril</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Athena, Azure, GCP, Spark, PySpark, Scala, Time Travel, dbt, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=3529dbf9c0179ae6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SpyCloud</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6795b407dce62c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Risk Data AI/ML Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,139 +3741,139 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=eea74f1dec514506</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, GCP, Kafka, MongoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b85fceb8179c41d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Gradient AI</t>
+          <t>SpyCloud</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15f0f7a6d40c320f</t>
+          <t>https://www.indeed.com/viewjob?jk=6795b407dce62c7f</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Corona del Mar, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72db0b65a035f06</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend &amp; Data</t>
+          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EPIC Kids</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Spark, Scala, Dimensional Modeling, Kimball, Star Schema, Fact Tables</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fa918834ca520e2</t>
+          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
         </is>
       </c>
     </row>
@@ -3968,17 +3968,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>Gradient AI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
+          <t>AWS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c053e495653c0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=15f0f7a6d40c320f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ffeb1ee043a99f0</t>
+          <t>https://www.indeed.com/viewjob?jk=9c053e495653c0e2</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Snowflake &amp; Data Platform Operations Engineer</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LendingTree</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dff6531dd274cbf5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ffeb1ee043a99f0</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
+          <t>Snowflake &amp; Data Platform Operations Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>LendingTree</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, Azure, Scala, Kafka, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
+          <t>https://www.indeed.com/viewjob?jk=dff6531dd274cbf5</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, GCP, Kafka, MongoDB, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5997f135ae7ff6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b85fceb8179c41d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Surt AI</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Corona del Mar, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed26f085dbb80ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e72db0b65a035f06</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Software Engineer, Backend &amp; Data</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mercari</t>
+          <t>EPIC Kids</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
+          <t>Hadoop, HDFS, Hive, HBase, Spark, Scala, Dimensional Modeling, Kimball, Star Schema, Fact Tables</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a998dd935be05c4</t>
+          <t>https://www.indeed.com/viewjob?jk=1fa918834ca520e2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=ab5997f135ae7ff6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Software Engineer - Rust &amp; Serverless (Remote)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Surt AI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, YARN, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Scala, DynamoDB, NoSQL, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56ed709de123ccd</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed26f085dbb80ff</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>within</t>
+          <t>Mercari</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1b8052c520238e</t>
+          <t>https://www.indeed.com/viewjob?jk=9a998dd935be05c4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Data-Driven Applications</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bde81135b1d2415c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SaaS Platform Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,29 +4371,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, YARN, SQL Server, PostgreSQL, MongoDB, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4503c0bae2650019</t>
+          <t>https://www.indeed.com/viewjob?jk=d56ed709de123ccd</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Konrad Group</t>
+          <t>within</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b59276e38a3792d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1b8052c520238e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Senior Software Engineer - Data-Driven Applications</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Vectra AI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Snowflake, PostgreSQL, MySQL, ELT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=bde81135b1d2415c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Product</t>
+          <t>SaaS Platform Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Art of Problem Solving Academy</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,29 +4476,29 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, MySQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6123e8fb6e4b9c03</t>
+          <t>https://www.indeed.com/viewjob?jk=4503c0bae2650019</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (ML Engineering)</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>Konrad Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, MLflow, AKS, Airflow, Git</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27775c7b5198786e</t>
+          <t>https://www.indeed.com/viewjob?jk=b59276e38a3792d8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Database Administrator</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Exiger</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b417041c5e167ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>The Knot Worldwide</t>
+          <t>Art of Problem Solving Academy</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,139 +4581,139 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Spark, PySpark, Dask, Polars, Snowflake, dbt, Tableau</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3866528c0c4c42f5</t>
+          <t>https://www.indeed.com/viewjob?jk=6123e8fb6e4b9c03</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data &amp; AI</t>
+          <t>Senior Data Scientist (ML Engineering)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ripple</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, MLflow, AKS, Airflow, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd25c09387615839</t>
+          <t>https://www.indeed.com/viewjob?jk=27775c7b5198786e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Marketplace Foundation</t>
+          <t>Senior Database Administrator</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Athena, S3, RDS, Azure, GCP, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fe7aa557db1f8b</t>
+          <t>https://www.indeed.com/viewjob?jk=b417041c5e167ad7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>The Knot Worldwide</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1447f0d619c40b</t>
+          <t>https://www.indeed.com/viewjob?jk=3866528c0c4c42f5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Platform Engineers</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a369ab2eae275c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e447be457217f98</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ccefe6b4cf39fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=fbac1edd00d90bb0</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Analytics Engineer, People Analytics</t>
+          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17dbbfe7334c8ce4</t>
+          <t>https://www.indeed.com/viewjob?jk=5116d23e81868b7b</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6915a31a656eea7e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1447f0d619c40b</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7217e6f4e824dd90</t>
+          <t>https://www.indeed.com/viewjob?jk=a369ab2eae275c5b</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e447be457217f98</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=6ccefe6b4cf39fcb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Credit Karma</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f31b874eb934bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=17dbbfe7334c8ce4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=698b540258cfcb66</t>
+          <t>https://www.indeed.com/viewjob?jk=6915a31a656eea7e</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning Platform</t>
+          <t>Analytics Engineer, People Analytics</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, dbt, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04016a73405055c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7217e6f4e824dd90</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer, Revenue Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>The New York Times</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Data Modeling, ETL, Pentaho, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68ff54cc645ee45</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Site Reliability/Data Engineer</t>
+          <t>Software Engineer II, Data &amp; AI</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Origis Energy</t>
+          <t>Ripple</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, MySQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, Athena, S3, API Gateway, ECS, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30b4bf646bfcd626</t>
+          <t>https://www.indeed.com/viewjob?jk=fd25c09387615839</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gallup</t>
+          <t>Credit Karma</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,34 +5176,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Snowflake, MySQL, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Dataflow, Hadoop, Spark, Scala, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fad735850fdd422</t>
+          <t>https://www.indeed.com/viewjob?jk=4f31b874eb934bcd</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, SQL Server, PostgreSQL, MySQL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6e0bde8c41e20a6</t>
+          <t>https://www.indeed.com/viewjob?jk=698b540258cfcb66</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Software Engineer, Machine Learning Platform</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, GCP, BigQuery, Scala, MLOps, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e14efc6b3a547f1</t>
+          <t>https://www.indeed.com/viewjob?jk=04016a73405055c1</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure</t>
+          <t>Data Engineer, Revenue Technology</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>The New York Times</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>El Segundo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,34 +5281,34 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>AWS, GCP, Scala, Data Modeling, ETL, Pentaho, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e01663940dc503</t>
+          <t>https://www.indeed.com/viewjob?jk=d68ff54cc645ee45</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Infrastructure</t>
+          <t>Site Reliability/Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GoGuardian</t>
+          <t>Origis Energy</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, MySQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a18245e7689460dc</t>
+          <t>https://www.indeed.com/viewjob?jk=30b4bf646bfcd626</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Graph Databases</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Hone health</t>
+          <t>Gallup</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Snowflake, MySQL, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c345200fd565a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7fad735850fdd422</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Graph Databases</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Hone health</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b93aab582e5c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6e0bde8c41e20a6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Flagship Pioneering, Inc.</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, S3, RDS, Scala, Snowflake, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=994eff426e58131c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e14efc6b3a547f1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Senior Software Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e01663940dc503</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Software Engineer - Infrastructure</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>GoGuardian</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, PostgreSQL, MySQL, Terraform, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81a07845c3146bdc</t>
+          <t>https://www.indeed.com/viewjob?jk=a18245e7689460dc</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Graph Databases</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Hone health</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40d4d8e83f705afd</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c345200fd565a8</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
+          <t>Senior Data Engineer, Graph Databases</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Hone health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbac1edd00d90bb0</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b93aab582e5c5f</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer, PAM &amp; Secrets</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Flagship Pioneering, Inc.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5116d23e81868b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=994eff426e58131c</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Platform Engineers</t>
+          <t>Senior Software Engineer - Marketplace Foundation</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, MongoDB, Cassandra, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
+          <t>https://www.indeed.com/viewjob?jk=37fe7aa557db1f8b</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=81a07845c3146bdc</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>BeyondTrust</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a615d3d337639a45</t>
+          <t>https://www.indeed.com/viewjob?jk=40d4d8e83f705afd</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chariot Energy</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a757d67b74798878</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Platform DevEx Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75a7e956c12bdc6a</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Platform DevEx Engineer</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=231b3551d1964b47</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Platform DevEx Engineer (DevOps)</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Black Canyon Consulting</t>
+          <t>BeyondTrust</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04691f1e7d928ccb</t>
+          <t>https://www.indeed.com/viewjob?jk=a615d3d337639a45</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer III (Back-end)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>inversion</t>
+          <t>Chariot Energy</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Playa Vista, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>S3, RDS, Azure, Data Factory, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d67473bb44960f85</t>
+          <t>https://www.indeed.com/viewjob?jk=a757d67b74798878</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Platform DevEx Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=75a7e956c12bdc6a</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Intern: Financial Systems Engineer</t>
+          <t>Platform DevEx Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EquipmentShare</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148277e432f8a247</t>
+          <t>https://www.indeed.com/viewjob?jk=231b3551d1964b47</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Senior Platform DevEx Engineer (DevOps)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Black Canyon Consulting</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,209 +6016,209 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Kafka, CI/CD, Kubernetes, AKS, Airflow</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=04691f1e7d928ccb</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III (Back-end)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>StockX</t>
+          <t>inversion</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Playa Vista, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Spark Streaming, Kafka, dbt, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269c9b47a6a44cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d67473bb44960f85</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0e12ad05e6f6ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Quality Platform Engineer</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Circle.so</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df725374039684f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Measurement &amp; Ads</t>
+          <t>Intern: Financial Systems Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>EquipmentShare</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, Snowflake, Data Modeling, dbt, Jenkins, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbf401730ca7f87</t>
+          <t>https://www.indeed.com/viewjob?jk=148277e432f8a247</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Bird Rides</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e321aa62ce282cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Automation &amp; Integration Developer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Professional Engineering Consultants</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hive, Scala, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d1937310481ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=f496e3f33567d8e1</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, MLOps</t>
+          <t>Automation &amp; Integration Developer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Path Robotics, Inc.</t>
+          <t>Professional Engineering Consultants</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd936db0ee5a06f</t>
+          <t>https://www.indeed.com/viewjob?jk=c144566d40a9779d</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>InStride</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7277f852b05ff55f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>TESSCO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,34 +6331,34 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=673a5bf1209ca871</t>
+          <t>https://www.indeed.com/viewjob?jk=61dbf36ce450d053</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Tableau Analyst</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Alpaca</t>
+          <t>Keeper Security</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>El Dorado Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757d74e2095c2c31</t>
+          <t>https://www.indeed.com/viewjob?jk=d83133d3b54a850e</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Solutions Engineer(Python/Airflow)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EDB</t>
+          <t>StockX</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Spark Streaming, Kafka, dbt, Airflow</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1362387d330626</t>
+          <t>https://www.indeed.com/viewjob?jk=269c9b47a6a44cf8</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Site Reliability</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>BABYLIST</t>
+          <t>InStride</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b9276905ba0f21</t>
+          <t>https://www.indeed.com/viewjob?jk=7277f852b05ff55f</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Site Reliability</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>BABYLIST</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Emeryville, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee049b023a70680</t>
+          <t>https://www.indeed.com/viewjob?jk=673a5bf1209ca871</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure (Federal)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Alpaca</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Spark, Scala, ETL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9482dc007d5f456</t>
+          <t>https://www.indeed.com/viewjob?jk=757d74e2095c2c31</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935bb71394d92d60</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1362387d330626</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Software Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>BABYLIST</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a44a84f2f8930db</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b9276905ba0f21</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
+          <t>Senior Software Engineer, Site Reliability</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>BABYLIST</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Emeryville, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,34 +6611,34 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Scala, MySQL, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c89d1883f151242</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee049b023a70680</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Infrastructure (Federal)</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Trivelta</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,34 +6646,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, Athena, BigQuery, Scala, Snowflake, ELT, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe224b36114f1f74</t>
+          <t>https://www.indeed.com/viewjob?jk=e9482dc007d5f456</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>peregrine technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, Tableau</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c5ad9d6af7101e</t>
+          <t>https://www.indeed.com/viewjob?jk=935bb71394d92d60</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>peregrine technologies</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90e473beb0de9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7a44a84f2f8930db</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Platform Engineer II (Terraform &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>peregrine technologies</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb739eafa098172</t>
+          <t>https://www.indeed.com/viewjob?jk=0c89d1883f151242</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior - Software Engineer - NetSuite Reporting/Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TESSCO</t>
+          <t>Trivelta</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Kinesis, Redshift, Athena, BigQuery, Scala, Snowflake, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dbf36ce450d053</t>
+          <t>https://www.indeed.com/viewjob?jk=fe224b36114f1f74</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer (Remote)</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>FortifyIQ</t>
+          <t>peregrine technologies</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Salem, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, MLOps, CI/CD, Airflow, Git, Python</t>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2286a631ab81c0c7</t>
+          <t>https://www.indeed.com/viewjob?jk=83c5ad9d6af7101e</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>peregrine technologies</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,29 +6856,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68de55a9dd8f6511</t>
+          <t>https://www.indeed.com/viewjob?jk=c90e473beb0de9b2</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - Weights &amp; Biases</t>
+          <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>peregrine technologies</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MLOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec6fe2aa83e84d26</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb739eafa098172</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Software Engineer Go Outdoors</t>
+          <t>Data &amp; AI Engineer (Remote)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Brandt Information Services, Inc.</t>
+          <t>FortifyIQ</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Salem, MA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, MLOps, CI/CD, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96e66828bc10e4bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2286a631ab81c0c7</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AI Integration Engineer, AI/ML</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Viral Nation</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57242a1632c106a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0e12ad05e6f6ea</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Delivery Solution Architect (US)</t>
+          <t>Senior Quality Platform Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Prophecy</t>
+          <t>Circle.so</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Texas City, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f8f6b81e67f67a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8df725374039684f</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Delivery Solution Architect (US)</t>
+          <t>Senior Software Engineer, Measurement &amp; Ads</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Prophecy</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ccd6881ad6a8a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbf401730ca7f87</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Bird Rides</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,29 +7066,29 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Hive, Spark, Kafka, Data Modeling, Star Schema, ETL, ELT, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025d7d48551febf2</t>
+          <t>https://www.indeed.com/viewjob?jk=e321aa62ce282cdf</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Frontend</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lila Sciences</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -7101,34 +7101,34 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Hive, Scala, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36be0146f5317a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1937310481ac7</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior Tableau Analyst</t>
+          <t>Senior Data Engineer, MLOps</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Path Robotics, Inc.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>El Dorado Hills, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, ETL, ELT, dbt, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d83133d3b54a850e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd936db0ee5a06f</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Software Engineer, Code Generation</t>
+          <t>Activation Solution Engineer- TMT/CBS</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MongoDB</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, HBase, Scala, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c31a324a7fdd053b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb564aaa33c98121</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, DevOps</t>
+          <t>Senior MuleSoft Developer - Austin, TX ONLY</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Parloa</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e609c5bc393ab2a6</t>
+          <t>https://www.indeed.com/viewjob?jk=68de55a9dd8f6511</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Metrics and Storage- Weights &amp; Biases</t>
+          <t>Software Engineer Go Outdoors</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Weights &amp; Biases</t>
+          <t>Brandt Information Services, Inc.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, MySQL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df212162e0fe3ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=96e66828bc10e4bb</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>AI Integration Engineer, AI/ML</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SentinelOne</t>
+          <t>Viral Nation</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,34 +7276,34 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
+          <t>IAM, RDS, GCP, Vertex AI, Scala, Snowflake, MLOps, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ad6be87c6e18e7</t>
+          <t>https://www.indeed.com/viewjob?jk=57242a1632c106a7</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Delivery Solution Architect (US)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>SentinelOne</t>
+          <t>Prophecy</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088631d63b72ebf1</t>
+          <t>https://www.indeed.com/viewjob?jk=2f8f6b81e67f67a4</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
+          <t>Delivery Solution Architect (US)</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IonQ</t>
+          <t>Prophecy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Spark, Scala, Snowflake, ETL, dbt</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=874999787fb11334</t>
+          <t>https://www.indeed.com/viewjob?jk=83ccd6881ad6a8a9</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Senior Software Systems Integration Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,34 +7381,34 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Spark, Scala, Data Modeling, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87ba6300acccca23</t>
+          <t>https://www.indeed.com/viewjob?jk=025d7d48551febf2</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Senior Software Systems Integration Engineer</t>
+          <t>Software Engineer, Code Generation</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>MongoDB</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Aliso Viejo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,34 +7416,34 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+          <t>AWS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094bed05b586255d</t>
+          <t>https://www.indeed.com/viewjob?jk=c31a324a7fdd053b</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Forward Deployed Engineer, DevOps</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>Parloa</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=e609c5bc393ab2a6</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Senior Software Engineer, Metrics and Storage- Weights &amp; Biases</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Weights &amp; Biases</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,34 +7486,34 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, MySQL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+          <t>https://www.indeed.com/viewjob?jk=df212162e0fe3ad2</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>SentinelOne</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=06ad6be87c6e18e7</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Tableau Engineer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>SentinelOne</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, Tableau, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, NoSQL, MLOps, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e80a48ce045ed33</t>
+          <t>https://www.indeed.com/viewjob?jk=088631d63b72ebf1</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AI Architect, Salesforce</t>
+          <t>Senior Infrastructure Software Engineer - Hardware Test</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Natera</t>
+          <t>IonQ</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, Snowflake, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71fa457437f2101d</t>
+          <t>https://www.indeed.com/viewjob?jk=874999787fb11334</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Taskrabbit</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955f461b0fdcc829</t>
+          <t>https://www.indeed.com/viewjob?jk=87ba6300acccca23</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Senior AI-Enabled Software Engineer in Test</t>
+          <t>Senior Software Systems Integration Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>eClinical Solutions, LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mansfield, MA, US USA</t>
+          <t>Aliso Viejo, CA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,15 +7661,295 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=094bed05b586255d</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Frontend</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36be0146f5317a2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Solutions Architect – Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SQL/Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Teradata Developer-5</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Tableau Engineer</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e80a48ce045ed33</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>AI Architect, Salesforce</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Natera</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, Snowflake, Terraform</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71fa457437f2101d</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Taskrabbit</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=955f461b0fdcc829</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Senior AI-Enabled Software Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>eClinical Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Mansfield, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, SQL Server, CI/CD, Docker, Kubernetes, Git, Datadog, Python</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27ad80ec756bf5da</t>
         </is>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Engineer - CDE</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, GCP, MLOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=ce062c1221d36aca</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Platform Engineer - CDE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Developer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JENSEN HUGHES</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a794a4fad5ad9bde</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Application Integration Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6129a30842f97a0c</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Oracle, MySQL, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866c80a990582061</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=28fad5a6eb6e90e7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=04a71202b47b41de</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vitol</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=b912b59e0b8d6118</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. Application Integration Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1672,11 +1672,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,94 +1686,94 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Platform Engineers</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Snowflake Admin-8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT System Administrator</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lexi Global</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Upland, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, NoSQL, ETL, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ebb702aee91dee</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineers</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>StockX</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, Scala, Spark Streaming, Kafka, dbt, Airflow</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a52d3ff88f626ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Activation Solution Engineer- TMT/CBS</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, HBase, Scala, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb564aaa33c98121</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Automation &amp; Integration Developer</t>
+          <t>Activation Solution Engineer- TMT/CBS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Professional Engineering Consultants</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, HBase, Scala, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f496e3f33567d8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=fb564aaa33c98121</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Automation &amp; Integration Developer</t>
+          <t>Solutions Architect – Cloud Platforms</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Professional Engineering Consultants</t>
+          <t>First Quality</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c144566d40a9779d</t>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Automation &amp; Integration Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>Professional Engineering Consultants</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b6cb8dfc375ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=f496e3f33567d8e1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Automation &amp; Integration Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Professional Engineering Consultants</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,42 +2386,2352 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+          <t>https://www.indeed.com/viewjob?jk=c144566d40a9779d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41b6cb8dfc375ac7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SQL/Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Teradata Developer-5</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Realign</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Plano, TX, US USA</t>
         </is>
       </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Winston-Salem, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Short Hills, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Virginia Beach, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Shreveport, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Providence, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Montvale, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Data Fabric Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RDS, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Power BI, Tableau, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98107848586892d4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-30.xlsx
+++ b/results/job_matches_2026-03-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.9</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=955ac0b1ad8a879b</t>
+          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
+          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1223c9ae7d10ef4</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Scala, Databricks Lakehouse, ELT, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc80464c8d3d0b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Platform Engineer - CDE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
+          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, GCP, MLOps</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce062c1221d36aca</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Platform Engineer - CDE</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Data Platform Engineer-7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-7</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,77 +1291,77 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=885a5728afb95e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
+          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28fad5a6eb6e90e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a71202b47b41de</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vitol</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b912b59e0b8d6118</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Application Integration Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,172 +1511,172 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GCP AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Python / Linux-7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1777,11 +1777,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,102 +1861,102 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96718ce206105693</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Snowflake Admin-8</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Cassandra, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f9277083b689a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Python / Linux-7</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, Jenkins, Maven, Terraform, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb205a4f0a2f4ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineers</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Activation Solution Engineer- TMT/CBS</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, HBase, Scala, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb564aaa33c98121</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Automation &amp; Integration Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Professional Engineering Consultants</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f496e3f33567d8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Automation &amp; Integration Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Professional Engineering Consultants</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c144566d40a9779d</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b6cb8dfc375ac7</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Teradata Developer-5</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Solutions Architect – Cloud Platforms</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>First Quality</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Teradata Developer-5</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,577 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Data Fabric Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98107848586892d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1daae7faefdba0a</t>
         </is>
       </c>
     </row>
